--- a/DataTables/DetailText/剧情/000_01完书.xlsx
+++ b/DataTables/DetailText/剧情/000_01完书.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCEF40C-4DA3-479A-9739-5E375F43B4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A185D8-A713-487F-9BB2-5DCFA6C60973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20490" yWindow="5280" windowWidth="20490" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>LineIndex</t>
   </si>
@@ -367,6 +367,10 @@
   </si>
   <si>
     <t>≥</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -520,7 +524,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -609,6 +613,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -914,7 +924,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
@@ -1180,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1194,7 +1204,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1219,8 +1229,11 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="33">
+      <c r="I1" s="31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1237,8 +1250,9 @@
       <c r="H2" s="29" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="26"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1259,8 +1273,9 @@
       <c r="H3" s="22" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="26"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1281,8 +1296,9 @@
       <c r="H4" s="26" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="26"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1301,8 +1317,9 @@
       <c r="H5" s="26" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="26"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1321,8 +1338,9 @@
       <c r="H6" s="30" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="26"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1331,6 +1349,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/DataTables/DetailText/剧情/000_01完书.xlsx
+++ b/DataTables/DetailText/剧情/000_01完书.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A185D8-A713-487F-9BB2-5DCFA6C60973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3A27AC-5305-4EFB-87F5-B8662EF57F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20490" yWindow="5280" windowWidth="20490" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -171,10 +171,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>李东璧去各地实地考察，采集样本，参考800多种书籍，花费27年，历经三次改写，至万历六年终于完成著作。全书共52卷，载药1892种，方剂11096首，插图图1109幅，约190万字。</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>李东璧</t>
     <phoneticPr fontId="9"/>
   </si>
@@ -371,6 +367,10 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>李东璧去各地实地考察，采集样本，参考800多种书籍，花费27年，历经三次改写，至万历六年终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -915,7 +915,7 @@
     </row>
     <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>31</v>
@@ -929,7 +929,7 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H2" s="22">
         <v>107</v>
@@ -1230,7 +1230,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="33">
@@ -1248,7 +1248,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I2" s="26"/>
     </row>
@@ -1260,18 +1260,18 @@
         <v>9</v>
       </c>
       <c r="C3" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="E3" s="27" t="s">
         <v>36</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>37</v>
       </c>
       <c r="F3" s="28"/>
       <c r="G3" s="27"/>
       <c r="H3" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I3" s="26"/>
     </row>
@@ -1283,18 +1283,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>40</v>
-      </c>
       <c r="E4" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="27"/>
       <c r="H4" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" s="26"/>
     </row>
@@ -1306,16 +1306,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>42</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>43</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
       <c r="H5" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5" s="26"/>
     </row>
@@ -1327,16 +1327,16 @@
         <v>9</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>43</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6" s="26"/>
     </row>
